--- a/music/pt2assignments.xlsx
+++ b/music/pt2assignments.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ben\School\Fall_2025\SOUnD\Wednesday\sound_sensor\music\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ben\Code\sound_sensor\music\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BFDD67-8B7F-49C6-B957-4D872DBFFC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039A8F85-2121-4DB3-B28D-FEE3886BE32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{68027898-88E3-45E1-97D4-6EE226E257BE}"/>
+    <workbookView xWindow="420" yWindow="516" windowWidth="14400" windowHeight="8304" xr2:uid="{68027898-88E3-45E1-97D4-6EE226E257BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -104,13 +104,13 @@
     <t>Lead Synth</t>
   </si>
   <si>
-    <t>Bass</t>
-  </si>
-  <si>
     <t>Piano</t>
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>Bass 2</t>
   </si>
 </sst>
 </file>
@@ -483,15 +483,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1678243A-5EA7-4509-B810-E9066275039D}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.140625" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -505,7 +505,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -519,7 +519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -530,10 +530,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -544,10 +544,10 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -561,7 +561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -575,7 +575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -589,7 +589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -600,45 +600,45 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
